--- a/exports/trend_1d/MAHABANK_full_report.xlsx
+++ b/exports/trend_1d/MAHABANK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,25 +557,25 @@
         <v>8.48</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42040</v>
+        <v>42041</v>
       </c>
       <c r="H2" t="n">
-        <v>40.65</v>
+        <v>40.35</v>
       </c>
       <c r="I2" t="n">
         <v>40.41055965</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="n">
-        <v>-7.93</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>8.27</v>
+        <v>9.31</v>
       </c>
       <c r="M2" t="n">
-        <v>0.46</v>
+        <v>0.62</v>
       </c>
       <c r="N2" t="n">
         <v>1.71</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>8.99</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42095</v>
+        <v>42100</v>
       </c>
       <c r="H3" t="n">
-        <v>37.65</v>
+        <v>38.1</v>
       </c>
       <c r="I3" t="n">
         <v>37.89170121725448</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K3" t="n">
-        <v>6.69</v>
+        <v>5.58</v>
       </c>
       <c r="L3" t="n">
         <v>4.09</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>9.49</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42123</v>
+        <v>42124</v>
       </c>
       <c r="H4" t="n">
-        <v>37.29</v>
+        <v>36.9</v>
       </c>
       <c r="I4" t="n">
         <v>36.90672999004519</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.13</v>
+        <v>-3.15</v>
       </c>
       <c r="L4" t="n">
         <v>4.09</v>
       </c>
       <c r="M4" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="N4" t="n">
         <v>2.68</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42138</v>
+        <v>42139</v>
       </c>
       <c r="H5" t="n">
-        <v>38</v>
+        <v>41.3</v>
       </c>
       <c r="I5" t="n">
         <v>39.60715855852536</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.98</v>
+        <v>-11.92</v>
       </c>
       <c r="L5" t="n">
-        <v>4.2</v>
+        <v>20.6</v>
       </c>
       <c r="M5" t="n">
-        <v>2.98</v>
+        <v>10.53</v>
       </c>
       <c r="N5" t="n">
-        <v>3.31</v>
+        <v>8.68</v>
       </c>
       <c r="O5" t="n">
         <v>-1.05</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>8.56</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42157</v>
+        <v>42158</v>
       </c>
       <c r="H6" t="n">
-        <v>37.9</v>
+        <v>36.35</v>
       </c>
       <c r="I6" t="n">
         <v>37.76344022349872</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.23</v>
+        <v>-11.99</v>
       </c>
       <c r="L6" t="n">
-        <v>9.199999999999999</v>
+        <v>12.59</v>
       </c>
       <c r="M6" t="n">
         <v>0.39</v>
       </c>
       <c r="N6" t="n">
-        <v>2.82</v>
+        <v>4.09</v>
       </c>
       <c r="O6" t="n">
         <v>8.68</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>13.68</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42201</v>
+        <v>42202</v>
       </c>
       <c r="H7" t="n">
-        <v>37.5</v>
+        <v>39.2</v>
       </c>
       <c r="I7" t="n">
         <v>38.8128538855777</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.16</v>
+        <v>-7.84</v>
       </c>
       <c r="L7" t="n">
         <v>13.62</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>11.44</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42228</v>
+        <v>42229</v>
       </c>
       <c r="H8" t="n">
-        <v>36.45</v>
+        <v>35</v>
       </c>
       <c r="I8" t="n">
         <v>35.89570045463685</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K8" t="n">
-        <v>-7.02</v>
+        <v>-10.71</v>
       </c>
       <c r="L8" t="n">
-        <v>7.42</v>
+        <v>12.88</v>
       </c>
       <c r="M8" t="n">
-        <v>0.52</v>
+        <v>2.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="O8" t="n">
         <v>4.53</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.97</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42339</v>
+        <v>42340</v>
       </c>
       <c r="H9" t="n">
-        <v>33.45</v>
+        <v>33.95</v>
       </c>
       <c r="I9" t="n">
         <v>33.87732843298643</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K9" t="n">
-        <v>4.43</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>8.57</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>8.83</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42348</v>
+        <v>42349</v>
       </c>
       <c r="H10" t="n">
-        <v>32.15</v>
+        <v>31.55</v>
       </c>
       <c r="I10" t="n">
         <v>31.57123058360584</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.3</v>
+        <v>-7.07</v>
       </c>
       <c r="L10" t="n">
-        <v>7.36</v>
+        <v>7.81</v>
       </c>
       <c r="M10" t="n">
         <v>1.11</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>10.36</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42409</v>
+        <v>42410</v>
       </c>
       <c r="H11" t="n">
-        <v>29.5</v>
+        <v>31.9</v>
       </c>
       <c r="I11" t="n">
         <v>31.02717407206802</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K11" t="n">
-        <v>6.5</v>
+        <v>-1.11</v>
       </c>
       <c r="L11" t="n">
         <v>6.18</v>
@@ -1068,7 +1199,7 @@
         <v>2.79</v>
       </c>
       <c r="N11" t="n">
-        <v>4.74</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>-1.87</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>16.68</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42508</v>
+        <v>42509</v>
       </c>
       <c r="H12" t="n">
-        <v>28.5</v>
+        <v>28.05</v>
       </c>
       <c r="I12" t="n">
         <v>28.30931235258455</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K12" t="n">
-        <v>-10.66</v>
+        <v>-12.07</v>
       </c>
       <c r="L12" t="n">
         <v>18.34</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>8.15</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42535</v>
+        <v>42536</v>
       </c>
       <c r="H13" t="n">
-        <v>29.2</v>
+        <v>29.75</v>
       </c>
       <c r="I13" t="n">
         <v>29.51707867411892</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.1</v>
+        <v>-6.06</v>
       </c>
       <c r="L13" t="n">
-        <v>6.42</v>
+        <v>6.6</v>
       </c>
       <c r="M13" t="n">
         <v>1.97</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.55</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42592</v>
+        <v>42593</v>
       </c>
       <c r="H14" t="n">
-        <v>31.4</v>
+        <v>31.05</v>
       </c>
       <c r="I14" t="n">
         <v>31.27005798866933</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K14" t="n">
-        <v>5.55</v>
+        <v>4.37</v>
       </c>
       <c r="L14" t="n">
         <v>1.34</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>7.5</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42620</v>
+        <v>42621</v>
       </c>
       <c r="H15" t="n">
-        <v>32.15</v>
+        <v>32.95</v>
       </c>
       <c r="I15" t="n">
         <v>32.79215513227854</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.54</v>
+        <v>-6.12</v>
       </c>
       <c r="L15" t="n">
-        <v>4.67</v>
+        <v>10.14</v>
       </c>
       <c r="M15" t="n">
         <v>1.47</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>7.97</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42641</v>
+        <v>42642</v>
       </c>
       <c r="H16" t="n">
-        <v>31.05</v>
+        <v>30.05</v>
       </c>
       <c r="I16" t="n">
         <v>30.32393065841208</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.77</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>6.83</v>
+        <v>9.56</v>
       </c>
       <c r="M16" t="n">
         <v>4.59</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>10.87</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42683</v>
+        <v>42684</v>
       </c>
       <c r="H17" t="n">
-        <v>28.3</v>
+        <v>30.95</v>
       </c>
       <c r="I17" t="n">
         <v>29.78213228346505</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K17" t="n">
-        <v>5.82</v>
+        <v>-3</v>
       </c>
       <c r="L17" t="n">
         <v>5.49</v>
@@ -1410,7 +1613,7 @@
         <v>3.59</v>
       </c>
       <c r="N17" t="n">
-        <v>1.96</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="O17" t="n">
         <v>-3.22</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>16.68</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42866</v>
+        <v>42867</v>
       </c>
       <c r="H18" t="n">
-        <v>35.1</v>
+        <v>33.95</v>
       </c>
       <c r="I18" t="n">
         <v>34.18688413455425</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K18" t="n">
-        <v>13.41</v>
+        <v>9.69</v>
       </c>
       <c r="L18" t="n">
         <v>9.210000000000001</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>14.43</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43032</v>
+        <v>43033</v>
       </c>
       <c r="H19" t="n">
-        <v>25.2</v>
+        <v>29.7</v>
       </c>
       <c r="I19" t="n">
         <v>26.10712740860291</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K19" t="n">
-        <v>25.77</v>
+        <v>12.52</v>
       </c>
       <c r="L19" t="n">
         <v>3.98</v>
       </c>
       <c r="M19" t="n">
-        <v>4.81</v>
+        <v>14.88</v>
       </c>
       <c r="N19" t="n">
-        <v>3.36</v>
+        <v>17.86</v>
       </c>
       <c r="O19" t="n">
         <v>-3.28</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>6</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>12.76</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43074</v>
+        <v>43075</v>
       </c>
       <c r="H20" t="n">
-        <v>26.4</v>
+        <v>25.65</v>
       </c>
       <c r="I20" t="n">
         <v>25.91172679903164</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K20" t="n">
-        <v>-11.11</v>
+        <v>-13.64</v>
       </c>
       <c r="L20" t="n">
-        <v>13.13</v>
+        <v>14.14</v>
       </c>
       <c r="M20" t="n">
         <v>2.07</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>13.34</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43308</v>
+        <v>43311</v>
       </c>
       <c r="H21" t="n">
-        <v>12.5</v>
+        <v>13.15</v>
       </c>
       <c r="I21" t="n">
         <v>13.05843253901729</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="K21" t="n">
-        <v>51.27</v>
+        <v>48.73</v>
       </c>
       <c r="L21" t="n">
         <v>4.09</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>161</v>
+        <v>162</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>9</v>
+      </c>
+      <c r="U21" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>10.57</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H22" t="n">
-        <v>12.5</v>
+        <v>12.15</v>
       </c>
       <c r="I22" t="n">
         <v>12.2542726232643</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.94</v>
+        <v>-7.6</v>
       </c>
       <c r="L22" t="n">
-        <v>6.46</v>
+        <v>7.98</v>
       </c>
       <c r="M22" t="n">
         <v>0.75</v>
       </c>
       <c r="N22" t="n">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="O22" t="n">
         <v>5.2</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>10.74</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43402</v>
+        <v>43403</v>
       </c>
       <c r="H23" t="n">
-        <v>11.6</v>
+        <v>13.9</v>
       </c>
       <c r="I23" t="n">
         <v>11.90404836304064</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K23" t="n">
-        <v>4.53</v>
+        <v>-14.4</v>
       </c>
       <c r="L23" t="n">
-        <v>5.76</v>
+        <v>14.4</v>
       </c>
       <c r="M23" t="n">
         <v>2.79</v>
       </c>
       <c r="N23" t="n">
-        <v>6.42</v>
+        <v>19.83</v>
       </c>
       <c r="O23" t="n">
         <v>-2.8</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>22.58</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43441</v>
+        <v>43444</v>
       </c>
       <c r="H24" t="n">
-        <v>12.55</v>
+        <v>12.15</v>
       </c>
       <c r="I24" t="n">
         <v>12.40847295371213</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K24" t="n">
-        <v>-9.710000000000001</v>
+        <v>-12.59</v>
       </c>
       <c r="L24" t="n">
         <v>16.55</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>12.6</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43452</v>
+        <v>43453</v>
       </c>
       <c r="H25" t="n">
-        <v>13.55</v>
+        <v>14.8</v>
       </c>
       <c r="I25" t="n">
         <v>13.68071394920846</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K25" t="n">
-        <v>-11.52</v>
+        <v>-21.81</v>
       </c>
       <c r="L25" t="n">
-        <v>14.81</v>
+        <v>27.16</v>
       </c>
       <c r="M25" t="n">
         <v>3.17</v>
       </c>
       <c r="N25" t="n">
-        <v>7.94</v>
+        <v>9.23</v>
       </c>
       <c r="O25" t="n">
         <v>-3.19</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>15.43</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43503</v>
+        <v>43504</v>
       </c>
       <c r="H26" t="n">
-        <v>13.75</v>
+        <v>13.5</v>
       </c>
       <c r="I26" t="n">
         <v>13.55748466945527</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K26" t="n">
-        <v>-7.09</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L26" t="n">
         <v>10.14</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>17.82</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43553</v>
+        <v>43556</v>
       </c>
       <c r="H27" t="n">
-        <v>13.75</v>
+        <v>14.3</v>
       </c>
       <c r="I27" t="n">
         <v>13.80307547502268</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.85</v>
+        <v>-5.93</v>
       </c>
       <c r="L27" t="n">
-        <v>3.33</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M27" t="n">
         <v>5.69</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43587</v>
+        <v>43588</v>
       </c>
       <c r="H28" t="n">
-        <v>16.75</v>
+        <v>16.35</v>
       </c>
       <c r="I28" t="n">
         <v>16.45190325435643</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K28" t="n">
-        <v>17.13</v>
+        <v>14.34</v>
       </c>
       <c r="L28" t="n">
         <v>3.5</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>20.55</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43767</v>
+        <v>43768</v>
       </c>
       <c r="H29" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="I29" t="n">
         <v>11.13948274598694</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K29" t="n">
-        <v>32.72</v>
+        <v>30.89</v>
       </c>
       <c r="L29" t="n">
         <v>4.59</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>6</v>
+      </c>
+      <c r="U29" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>16.25</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43862</v>
+        <v>43864</v>
       </c>
       <c r="H30" t="n">
-        <v>12.65</v>
+        <v>12.25</v>
       </c>
       <c r="I30" t="n">
         <v>12.58149844247035</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K30" t="n">
-        <v>11.95</v>
+        <v>8.41</v>
       </c>
       <c r="L30" t="n">
         <v>2.65</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>15.61</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43983</v>
+        <v>43984</v>
       </c>
       <c r="H31" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="I31" t="n">
         <v>9.412926160595967</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K31" t="n">
-        <v>25.71</v>
+        <v>21.63</v>
       </c>
       <c r="L31" t="n">
         <v>4.08</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>13.29</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44081</v>
+        <v>44082</v>
       </c>
       <c r="H32" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="I32" t="n">
         <v>12.60255605846935</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K32" t="n">
-        <v>32.29</v>
+        <v>29.17</v>
       </c>
       <c r="L32" t="n">
         <v>5.21</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>18.61</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44161</v>
+        <v>44162</v>
       </c>
       <c r="H33" t="n">
-        <v>11.8</v>
+        <v>12.2</v>
       </c>
       <c r="I33" t="n">
         <v>12.00631112243691</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K33" t="n">
-        <v>4.84</v>
+        <v>1.61</v>
       </c>
       <c r="L33" t="n">
         <v>4.84</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>9.25</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44182</v>
+        <v>44183</v>
       </c>
       <c r="H34" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="I34" t="n">
         <v>13.66531670628826</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>12.3</v>
+        <v>9.84</v>
       </c>
       <c r="L34" t="n">
         <v>3.28</v>
       </c>
       <c r="M34" t="n">
-        <v>-0</v>
+        <v>0.73</v>
       </c>
       <c r="N34" t="n">
         <v>5.79</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>15.09</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44207</v>
+        <v>44208</v>
       </c>
       <c r="H35" t="n">
-        <v>13.85</v>
+        <v>14.8</v>
       </c>
       <c r="I35" t="n">
         <v>14.69657572298493</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.36</v>
+        <v>-10.45</v>
       </c>
       <c r="L35" t="n">
-        <v>8.210000000000001</v>
+        <v>15.67</v>
       </c>
       <c r="M35" t="n">
         <v>3.41</v>
       </c>
       <c r="N35" t="n">
-        <v>6.02</v>
+        <v>6.86</v>
       </c>
       <c r="O35" t="n">
         <v>-2.19</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>16.74</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44218</v>
+        <v>44221</v>
       </c>
       <c r="H36" t="n">
-        <v>14.45</v>
+        <v>13.6</v>
       </c>
       <c r="I36" t="n">
         <v>13.75781127209015</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.36</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>7.43</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M36" t="n">
         <v>1.01</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>23.59</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44242</v>
+        <v>44243</v>
       </c>
       <c r="H37" t="n">
-        <v>15.9</v>
+        <v>19.05</v>
       </c>
       <c r="I37" t="n">
         <v>16.58222752438165</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K37" t="n">
-        <v>-16.91</v>
+        <v>-40.07</v>
       </c>
       <c r="L37" t="n">
-        <v>23.9</v>
+        <v>40.07</v>
       </c>
       <c r="M37" t="n">
-        <v>7.14</v>
+        <v>15.09</v>
       </c>
       <c r="N37" t="n">
-        <v>4.91</v>
+        <v>19.81</v>
       </c>
       <c r="O37" t="n">
         <v>-5.88</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>19.17</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44271</v>
+        <v>44272</v>
       </c>
       <c r="H38" t="n">
-        <v>21.4</v>
+        <v>20.55</v>
       </c>
       <c r="I38" t="n">
         <v>21.00763564475938</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K38" t="n">
-        <v>12.34</v>
+        <v>7.87</v>
       </c>
       <c r="L38" t="n">
         <v>7.35</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>26.95</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44294</v>
+        <v>44295</v>
       </c>
       <c r="H39" t="n">
-        <v>21.2</v>
+        <v>24.75</v>
       </c>
       <c r="I39" t="n">
         <v>23.994285007372</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.16</v>
+        <v>-20.44</v>
       </c>
       <c r="L39" t="n">
-        <v>11.92</v>
+        <v>23.6</v>
       </c>
       <c r="M39" t="n">
         <v>8.35</v>
       </c>
       <c r="N39" t="n">
-        <v>9.970000000000001</v>
+        <v>16.75</v>
       </c>
       <c r="O39" t="n">
         <v>-3.97</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>24.8</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44364</v>
+        <v>44365</v>
       </c>
       <c r="H40" t="n">
-        <v>25.45</v>
+        <v>25.1</v>
       </c>
       <c r="I40" t="n">
         <v>25.12986098730693</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K40" t="n">
-        <v>2.83</v>
+        <v>1.41</v>
       </c>
       <c r="L40" t="n">
         <v>13.33</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>15.86</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44470</v>
+        <v>44473</v>
       </c>
       <c r="H41" t="n">
-        <v>20</v>
+        <v>20.15</v>
       </c>
       <c r="I41" t="n">
         <v>20.11352096454024</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K41" t="n">
-        <v>20.32</v>
+        <v>19.72</v>
       </c>
       <c r="L41" t="n">
         <v>10.36</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>5</v>
+      </c>
+      <c r="U41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>12.23</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H42" t="n">
-        <v>19.8</v>
+        <v>19.2</v>
       </c>
       <c r="I42" t="n">
         <v>19.46920793675115</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.74</v>
+        <v>-4.71</v>
       </c>
       <c r="L42" t="n">
-        <v>2.23</v>
+        <v>5.46</v>
       </c>
       <c r="M42" t="n">
         <v>0.24</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>12.78</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44575</v>
+        <v>44578</v>
       </c>
       <c r="H43" t="n">
-        <v>20.9</v>
+        <v>21.05</v>
       </c>
       <c r="I43" t="n">
         <v>20.98388556467085</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K43" t="n">
-        <v>-8.85</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="L43" t="n">
         <v>11.72</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>8.56</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44603</v>
+        <v>44606</v>
       </c>
       <c r="H44" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="I44" t="n">
         <v>19.24819791672594</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K44" t="n">
-        <v>-5.94</v>
+        <v>-9.74</v>
       </c>
       <c r="L44" t="n">
-        <v>9.029999999999999</v>
+        <v>10.69</v>
       </c>
       <c r="M44" t="n">
-        <v>1.98</v>
+        <v>2.53</v>
       </c>
       <c r="N44" t="n">
-        <v>3.93</v>
+        <v>4.04</v>
       </c>
       <c r="O44" t="n">
         <v>0.72</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>13.58</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44657</v>
+        <v>44658</v>
       </c>
       <c r="H45" t="n">
-        <v>18.75</v>
+        <v>18.85</v>
       </c>
       <c r="I45" t="n">
         <v>18.81608240811699</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K45" t="n">
-        <v>1.32</v>
+        <v>0.79</v>
       </c>
       <c r="L45" t="n">
         <v>3.68</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>12.79</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44691</v>
+        <v>44692</v>
       </c>
       <c r="H46" t="n">
-        <v>16.45</v>
+        <v>15.9</v>
       </c>
       <c r="I46" t="n">
         <v>16.43853379295801</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K46" t="n">
-        <v>-12.73</v>
+        <v>-15.65</v>
       </c>
       <c r="L46" t="n">
-        <v>14.59</v>
+        <v>17.77</v>
       </c>
       <c r="M46" t="n">
         <v>1.17</v>
       </c>
       <c r="N46" t="n">
-        <v>2.82</v>
+        <v>3.34</v>
       </c>
       <c r="O46" t="n">
         <v>0.53</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>13.8</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44708</v>
+        <v>44711</v>
       </c>
       <c r="H47" t="n">
-        <v>16.5</v>
+        <v>17.6</v>
       </c>
       <c r="I47" t="n">
         <v>17.44667608420593</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.77</v>
+        <v>-10.69</v>
       </c>
       <c r="L47" t="n">
-        <v>4.4</v>
+        <v>11.32</v>
       </c>
       <c r="M47" t="n">
         <v>1.94</v>
       </c>
       <c r="N47" t="n">
-        <v>3.86</v>
+        <v>6.67</v>
       </c>
       <c r="O47" t="n">
         <v>-3.34</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>14.08</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44727</v>
+        <v>44728</v>
       </c>
       <c r="H48" t="n">
-        <v>16.25</v>
+        <v>15.75</v>
       </c>
       <c r="I48" t="n">
         <v>15.81915648903724</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K48" t="n">
-        <v>-7.67</v>
+        <v>-10.51</v>
       </c>
       <c r="L48" t="n">
-        <v>10.51</v>
+        <v>11.65</v>
       </c>
       <c r="M48" t="n">
         <v>2.16</v>
       </c>
       <c r="N48" t="n">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="O48" t="n">
         <v>6.67</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>12.3</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44761</v>
+        <v>44762</v>
       </c>
       <c r="H49" t="n">
-        <v>16.9</v>
+        <v>17.05</v>
       </c>
       <c r="I49" t="n">
         <v>16.90658627753421</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K49" t="n">
-        <v>-7.3</v>
+        <v>-8.25</v>
       </c>
       <c r="L49" t="n">
-        <v>8.25</v>
+        <v>9.52</v>
       </c>
       <c r="M49" t="n">
         <v>1.86</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.34</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H50" t="n">
-        <v>18.15</v>
+        <v>17.2</v>
       </c>
       <c r="I50" t="n">
         <v>18.09299676565182</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K50" t="n">
-        <v>6.45</v>
+        <v>0.88</v>
       </c>
       <c r="L50" t="n">
         <v>3.23</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>13.91</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44852</v>
+        <v>44853</v>
       </c>
       <c r="H51" t="n">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="I51" t="n">
         <v>19.33057247587568</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K51" t="n">
-        <v>-11.05</v>
+        <v>-12.79</v>
       </c>
       <c r="L51" t="n">
-        <v>13.08</v>
+        <v>14.83</v>
       </c>
       <c r="M51" t="n">
         <v>2.56</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>8.57</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H52" t="n">
-        <v>28.85</v>
+        <v>26.1</v>
       </c>
       <c r="I52" t="n">
         <v>28.48429854278163</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K52" t="n">
-        <v>48.71</v>
+        <v>34.54</v>
       </c>
       <c r="L52" t="n">
         <v>1.55</v>
       </c>
       <c r="M52" t="n">
-        <v>0.99</v>
+        <v>1.56</v>
       </c>
       <c r="N52" t="n">
-        <v>8.970000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="O52" t="n">
         <v>1.57</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>34.03</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45026</v>
+        <v>45027</v>
       </c>
       <c r="H53" t="n">
-        <v>26.15</v>
+        <v>26.7</v>
       </c>
       <c r="I53" t="n">
         <v>26.2431155958925</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.19</v>
+        <v>-2.3</v>
       </c>
       <c r="L53" t="n">
         <v>31.99</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>5</v>
+      </c>
+      <c r="U53" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>11.08</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45085</v>
+        <v>45086</v>
       </c>
       <c r="H54" t="n">
-        <v>30.35</v>
+        <v>28.35</v>
       </c>
       <c r="I54" t="n">
         <v>29.10004063454267</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K54" t="n">
-        <v>13.67</v>
+        <v>6.18</v>
       </c>
       <c r="L54" t="n">
         <v>1.69</v>
@@ -3519,7 +4166,7 @@
         <v>3.19</v>
       </c>
       <c r="N54" t="n">
-        <v>3.83</v>
+        <v>6.59</v>
       </c>
       <c r="O54" t="n">
         <v>2.1</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>13.4</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45107</v>
+        <v>45110</v>
       </c>
       <c r="H55" t="n">
-        <v>28.9</v>
+        <v>29.95</v>
       </c>
       <c r="I55" t="n">
         <v>29.18563173955157</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.94</v>
+        <v>-5.64</v>
       </c>
       <c r="L55" t="n">
-        <v>5.82</v>
+        <v>7.23</v>
       </c>
       <c r="M55" t="n">
-        <v>0.72</v>
+        <v>0.87</v>
       </c>
       <c r="N55" t="n">
         <v>3.64</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.17</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H56" t="n">
-        <v>43.8</v>
+        <v>40.35</v>
       </c>
       <c r="I56" t="n">
         <v>42.46505122478827</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K56" t="n">
-        <v>46.24</v>
+        <v>34.72</v>
       </c>
       <c r="L56" t="n">
         <v>2.84</v>
@@ -3633,7 +4304,7 @@
         <v>2.16</v>
       </c>
       <c r="N56" t="n">
-        <v>7.22</v>
+        <v>7.88</v>
       </c>
       <c r="O56" t="n">
         <v>3.63</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>21.19</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45274</v>
+        <v>45275</v>
       </c>
       <c r="H57" t="n">
-        <v>46.75</v>
+        <v>47.35</v>
       </c>
       <c r="I57" t="n">
         <v>47.03740158737492</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K57" t="n">
-        <v>-15.86</v>
+        <v>-17.35</v>
       </c>
       <c r="L57" t="n">
         <v>18.96</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45331</v>
+        <v>45334</v>
       </c>
       <c r="H58" t="n">
-        <v>61.55</v>
+        <v>55.3</v>
       </c>
       <c r="I58" t="n">
         <v>55.58732978581161</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K58" t="n">
-        <v>29.99</v>
+        <v>16.79</v>
       </c>
       <c r="L58" t="n">
         <v>9.08</v>
@@ -3747,7 +4442,7 @@
         <v>0.45</v>
       </c>
       <c r="N58" t="n">
-        <v>6.8</v>
+        <v>10.15</v>
       </c>
       <c r="O58" t="n">
         <v>1.28</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>28.54</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="H59" t="n">
-        <v>65.25</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I59" t="n">
         <v>65.60886942461457</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K59" t="n">
-        <v>-17.99</v>
+        <v>-20.98</v>
       </c>
       <c r="L59" t="n">
-        <v>20.34</v>
+        <v>21.7</v>
       </c>
       <c r="M59" t="n">
         <v>1.68</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>13.13</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="H60" t="n">
-        <v>63.9</v>
+        <v>62.5</v>
       </c>
       <c r="I60" t="n">
         <v>63.13287361907435</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.48</v>
+        <v>-6.58</v>
       </c>
       <c r="L60" t="n">
         <v>11.51</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>12.7</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c r="H61" t="n">
-        <v>68.15000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I61" t="n">
         <v>70.43630069566446</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K61" t="n">
-        <v>-9.039999999999999</v>
+        <v>-12.96</v>
       </c>
       <c r="L61" t="n">
-        <v>12.48</v>
+        <v>14.4</v>
       </c>
       <c r="M61" t="n">
         <v>0.74</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>11</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H62" t="n">
-        <v>72.5</v>
+        <v>63.3</v>
       </c>
       <c r="I62" t="n">
         <v>63.76849580954595</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K62" t="n">
-        <v>2.69</v>
+        <v>-10.34</v>
       </c>
       <c r="L62" t="n">
-        <v>5.81</v>
+        <v>16.43</v>
       </c>
       <c r="M62" t="n">
         <v>1.16</v>
       </c>
       <c r="N62" t="n">
-        <v>2.55</v>
+        <v>12.69</v>
       </c>
       <c r="O62" t="n">
         <v>3.6</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>21.47</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45485</v>
+        <v>45488</v>
       </c>
       <c r="H63" t="n">
-        <v>65.08</v>
+        <v>68.75</v>
       </c>
       <c r="I63" t="n">
         <v>68.25163731794797</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.81</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L63" t="n">
         <v>13.74</v>
@@ -4032,7 +4787,7 @@
         <v>1.5</v>
       </c>
       <c r="N63" t="n">
-        <v>3.61</v>
+        <v>5.64</v>
       </c>
       <c r="O63" t="n">
         <v>-12.69</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>11.64</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H64" t="n">
-        <v>65.51000000000001</v>
+        <v>62.17</v>
       </c>
       <c r="I64" t="n">
         <v>62.2331336371124</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K64" t="n">
-        <v>-4.71</v>
+        <v>-9.57</v>
       </c>
       <c r="L64" t="n">
-        <v>8.470000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="M64" t="n">
-        <v>1.95</v>
+        <v>2.78</v>
       </c>
       <c r="N64" t="n">
-        <v>2.29</v>
+        <v>5.1</v>
       </c>
       <c r="O64" t="n">
         <v>5.64</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>12.6</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45555</v>
+        <v>45558</v>
       </c>
       <c r="H65" t="n">
-        <v>58.42</v>
+        <v>63.12</v>
       </c>
       <c r="I65" t="n">
         <v>62.89555000558857</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K65" t="n">
-        <v>6.03</v>
+        <v>-1.53</v>
       </c>
       <c r="L65" t="n">
         <v>3.2</v>
@@ -4146,7 +4925,7 @@
         <v>1.59</v>
       </c>
       <c r="N65" t="n">
-        <v>3.92</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O65" t="n">
         <v>-5.1</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>12.1</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H66" t="n">
-        <v>57.65</v>
+        <v>55.84</v>
       </c>
       <c r="I66" t="n">
         <v>56.5701886422788</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K66" t="n">
-        <v>-8.67</v>
+        <v>-11.53</v>
       </c>
       <c r="L66" t="n">
-        <v>9.050000000000001</v>
+        <v>11.91</v>
       </c>
       <c r="M66" t="n">
         <v>1.47</v>
       </c>
       <c r="N66" t="n">
-        <v>2.63</v>
+        <v>3.14</v>
       </c>
       <c r="O66" t="n">
         <v>8.050000000000001</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>12.43</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45601</v>
+        <v>45602</v>
       </c>
       <c r="H67" t="n">
-        <v>55.65</v>
+        <v>55.91</v>
       </c>
       <c r="I67" t="n">
         <v>55.67791415580702</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K67" t="n">
-        <v>0.34</v>
+        <v>-0.13</v>
       </c>
       <c r="L67" t="n">
         <v>5.43</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>11.86</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45643</v>
+        <v>45644</v>
       </c>
       <c r="H68" t="n">
-        <v>54.99</v>
+        <v>53.34</v>
       </c>
       <c r="I68" t="n">
         <v>53.37344648455456</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.65</v>
+        <v>-4.6</v>
       </c>
       <c r="L68" t="n">
         <v>11.27</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>10.73</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="H69" t="n">
-        <v>48.4</v>
+        <v>50.9</v>
       </c>
       <c r="I69" t="n">
         <v>49.02827980522731</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="K69" t="n">
-        <v>9.26</v>
+        <v>4.57</v>
       </c>
       <c r="L69" t="n">
         <v>5.55</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>5</v>
+      </c>
+      <c r="U69" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>11.9</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45875</v>
+        <v>45876</v>
       </c>
       <c r="H70" t="n">
-        <v>53.96</v>
+        <v>53.57</v>
       </c>
       <c r="I70" t="n">
         <v>53.7485990415959</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K70" t="n">
-        <v>6.01</v>
+        <v>5.25</v>
       </c>
       <c r="L70" t="n">
         <v>6.66</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>5</v>
+      </c>
+      <c r="U70" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>6.1</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="H71" t="n">
-        <v>55.06</v>
+        <v>57.31</v>
       </c>
       <c r="I71" t="n">
         <v>55.33956217895391</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K71" t="n">
-        <v>-2.78</v>
+        <v>-6.98</v>
       </c>
       <c r="L71" t="n">
-        <v>5</v>
+        <v>7.26</v>
       </c>
       <c r="M71" t="n">
         <v>1.31</v>
       </c>
       <c r="N71" t="n">
-        <v>3.9</v>
+        <v>4.09</v>
       </c>
       <c r="O71" t="n">
         <v>-0.72</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="H72" t="n">
-        <v>65.27</v>
+        <v>60.43</v>
       </c>
       <c r="I72" t="n">
         <v>61.77912661565371</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K72" t="n">
-        <v>13.89</v>
+        <v>5.44</v>
       </c>
       <c r="L72" t="n">
         <v>6.04</v>
@@ -4545,7 +5408,7 @@
         <v>2.19</v>
       </c>
       <c r="N72" t="n">
-        <v>4.29</v>
+        <v>7.42</v>
       </c>
       <c r="O72" t="n">
         <v>4.09</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>6</v>
+      </c>
+      <c r="U72" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>14.64</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="H73" t="n">
-        <v>67.3</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="I73" t="n">
         <v>68.35693210714547</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K73" t="n">
-        <v>-11.37</v>
+        <v>-14.17</v>
       </c>
       <c r="L73" t="n">
-        <v>12.03</v>
+        <v>14.53</v>
       </c>
       <c r="M73" t="n">
         <v>4.32</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>9.77</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H74" t="n">
-        <v>70.13</v>
+        <v>65.69</v>
       </c>
       <c r="I74" t="n">
         <v>68.06434261340986</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K74" t="n">
-        <v>1.65</v>
+        <v>-4.78</v>
       </c>
       <c r="L74" t="n">
-        <v>2.57</v>
+        <v>7.83</v>
       </c>
       <c r="M74" t="n">
         <v>5.5</v>
       </c>
       <c r="N74" t="n">
-        <v>4.95</v>
+        <v>6.33</v>
       </c>
       <c r="O74" t="n">
         <v>2.51</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>14.32</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H75" t="n">
-        <v>70.14</v>
+        <v>71.39</v>
       </c>
       <c r="I75" t="n">
         <v>71.05019824986074</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K75" t="n">
-        <v>-6.77</v>
+        <v>-8.68</v>
       </c>
       <c r="L75" t="n">
-        <v>8.77</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M75" t="n">
         <v>4.45</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>11.71</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="H76" t="n">
-        <v>86.51000000000001</v>
+        <v>83.19</v>
       </c>
       <c r="I76" t="n">
         <v>83.6257673115386</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K76" t="n">
-        <v>21.18</v>
+        <v>16.53</v>
       </c>
       <c r="L76" t="n">
         <v>1.51</v>
@@ -4773,7 +5684,7 @@
         <v>3.45</v>
       </c>
       <c r="N76" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="O76" t="n">
         <v>1.78</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>12.97</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="H77" t="n">
-        <v>81.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I77" t="n">
         <v>83.68560334877512</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K77" t="n">
-        <v>1.79</v>
+        <v>-2.9</v>
       </c>
       <c r="L77" t="n">
         <v>5.13</v>
@@ -4830,7 +5753,7 @@
         <v>1.09</v>
       </c>
       <c r="N77" t="n">
-        <v>3.7</v>
+        <v>4.77</v>
       </c>
       <c r="O77" t="n">
         <v>-3.84</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4866,22 +5801,22 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="H78" t="n">
-        <v>80.84999999999999</v>
+        <v>79.16</v>
       </c>
       <c r="I78" t="n">
         <v>79.25646335108421</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K78" t="n">
-        <v>-5.55</v>
+        <v>-7.52</v>
       </c>
       <c r="L78" t="n">
-        <v>7.48</v>
+        <v>7.52</v>
       </c>
       <c r="M78" t="n">
         <v>0.65</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,14 @@
       <c r="Q79" t="n">
         <v>20</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9905,7 +10860,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.8</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="6">
@@ -9915,7 +10870,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -9925,7 +10880,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8">
@@ -9935,7 +10890,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -9945,7 +10900,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -9955,7 +10910,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>109.4</v>
+        <v>111.4</v>
       </c>
     </row>
     <row r="11">
@@ -9995,7 +10950,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.86</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="15">
@@ -10005,7 +10960,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.18</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="16">
@@ -10015,7 +10970,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="17">
@@ -10025,7 +10980,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>51.27</v>
+        <v>48.73</v>
       </c>
     </row>
     <row r="18">
@@ -10035,7 +10990,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.2</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="19">
@@ -10045,7 +11000,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.17</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="20">
@@ -10055,7 +11010,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.83</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="21">
@@ -10065,7 +11020,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31.99</v>
+        <v>40.07</v>
       </c>
     </row>
     <row r="22">
@@ -10075,7 +11030,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
@@ -10085,7 +11040,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
@@ -10095,7 +11050,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.84</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="25">
@@ -10105,7 +11060,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.460000000000001</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="26">
@@ -10115,7 +11070,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.21</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="27">
@@ -10125,7 +11080,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14.08</v>
+        <v>19.83</v>
       </c>
     </row>
     <row r="28">
@@ -10135,7 +11090,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29">
